--- a/uploads/lab_rooms.xlsx
+++ b/uploads/lab_rooms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC475C51-BFBA-495C-935E-0EDD1EBE3AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA2D88-68FF-49F2-AA2A-F24AB52264E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C81C6726-5086-4F86-A491-46F0D6D31795}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="87">
   <si>
     <t>class</t>
   </si>
@@ -257,9 +257,6 @@
     <t>A507</t>
   </si>
   <si>
-    <t>A507,102</t>
-  </si>
-  <si>
     <t>A507,A501</t>
   </si>
   <si>
@@ -284,16 +281,25 @@
     <t>A401,A205</t>
   </si>
   <si>
-    <t>A401,A507</t>
-  </si>
-  <si>
-    <t>A401,102</t>
-  </si>
-  <si>
-    <t>A,A507</t>
-  </si>
-  <si>
-    <t>A401B,A507</t>
+    <t>CP LAB/IT W/S</t>
+  </si>
+  <si>
+    <t>A401A,A510</t>
+  </si>
+  <si>
+    <t>A401A,A402A</t>
+  </si>
+  <si>
+    <t>A402A,A510</t>
+  </si>
+  <si>
+    <t>A401A,A507</t>
+  </si>
+  <si>
+    <t>A401B,A401A</t>
+  </si>
+  <si>
+    <t>A401B</t>
   </si>
 </sst>
 </file>
@@ -709,7 +715,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -720,7 +726,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -775,7 +781,7 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -797,7 +803,7 @@
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -808,7 +814,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -819,7 +825,7 @@
         <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -827,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -841,7 +847,7 @@
         <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -852,7 +858,7 @@
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -863,7 +869,7 @@
         <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -874,7 +880,7 @@
         <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -885,7 +891,7 @@
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -896,7 +902,7 @@
         <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -907,7 +913,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -940,7 +946,7 @@
         <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -951,7 +957,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -962,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -973,7 +979,7 @@
         <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -984,7 +990,7 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -995,7 +1001,7 @@
         <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1006,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1017,7 +1023,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1061,7 +1067,7 @@
         <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -1083,7 +1089,7 @@
         <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -1094,7 +1100,7 @@
         <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -1105,7 +1111,7 @@
         <v>33</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -1149,7 +1155,7 @@
         <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -1160,7 +1166,7 @@
         <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="18" x14ac:dyDescent="0.35">
